--- a/scripts/fixtures/cancellations_with_status.xlsx
+++ b/scripts/fixtures/cancellations_with_status.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="CANCELLATIONS" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SALES" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO8"/>
+  <dimension ref="A1:AN8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -599,25 +600,20 @@
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Processed Date</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>Processed Date</t>
+          <t>Revio Status</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>Revio Status</t>
+          <t>Casi Status</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
-        <is>
-          <t>Casi Status</t>
-        </is>
-      </c>
-      <c r="AO1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -661,7 +657,11 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>8501010001234</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
@@ -674,17 +674,12 @@
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>27821111111</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
           <t>2026-04-25 10:00:00 SAST</t>
         </is>
       </c>
+      <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -724,7 +719,11 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>8502020002345</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
@@ -735,15 +734,10 @@
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>0822222222</t>
-        </is>
-      </c>
+      <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
@@ -783,7 +777,11 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>7503030003456</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
@@ -794,15 +792,10 @@
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>0833333333</t>
-        </is>
-      </c>
+      <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -838,7 +831,11 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>8504040004567</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
@@ -849,15 +846,10 @@
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>27844444444</t>
-        </is>
-      </c>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -897,7 +889,11 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>8505050005678</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
@@ -908,15 +904,10 @@
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>0855555555</t>
-        </is>
-      </c>
+      <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -956,7 +947,11 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>8506060006789</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
@@ -971,7 +966,6 @@
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -1011,7 +1005,11 @@
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>8507070007890</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
@@ -1022,13 +1020,120 @@
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="n">
-        <v>821234567</v>
-      </c>
+      <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>account number</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>phone_number</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>IDENTITY_OR_REG_NUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>87000000002</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0822222222</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>8502020002345</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>99999999003</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0833333333</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>7503030003456</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>87000000004</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>821234567</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>8504040004567</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>87000000007</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>abc-def-ghij</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>8507070007890</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>87000000999</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>9999999999999</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
